--- a/brand_rules.xlsx
+++ b/brand_rules.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
   <si>
     <t>keyword</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Ulefone</t>
+  </si>
+  <si>
+    <t>Ulfone</t>
   </si>
   <si>
     <t>TCL</t>
@@ -1288,7 +1291,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1496,7 +1499,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1585,6 +1588,14 @@
       </c>
       <c r="B37" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/brand_rules.xlsx
+++ b/brand_rules.xlsx
@@ -29,10 +29,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
   <si>
-    <t>keyword</t>
-  </si>
-  <si>
-    <t>brand</t>
+    <t>关键词</t>
+  </si>
+  <si>
+    <t>标准品牌</t>
   </si>
   <si>
     <t>iPhone</t>

--- a/brand_rules.xlsx
+++ b/brand_rules.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
   <si>
     <t>关键词</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>MOTO</t>
+  </si>
+  <si>
+    <t>Motorola</t>
   </si>
   <si>
     <t>Google</t>
@@ -1291,7 +1294,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1379,7 +1382,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1427,7 +1430,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1435,7 +1438,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1499,7 +1502,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1507,7 +1510,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1596,6 +1599,14 @@
       </c>
       <c r="B38" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/brand_rules.xlsx
+++ b/brand_rules.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
   <si>
     <t>关键词</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Google</t>
+  </si>
+  <si>
+    <t>Pixel</t>
   </si>
   <si>
     <t>OnePlus</t>
@@ -1294,7 +1297,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1323,63 +1326,63 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -1387,55 +1390,55 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
@@ -1443,71 +1446,71 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
@@ -1515,98 +1518,114 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/brand_rules.xlsx
+++ b/brand_rules.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="43">
   <si>
     <t>关键词</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>Boost Mobile</t>
+  </si>
+  <si>
+    <t>Boost</t>
   </si>
   <si>
     <t>Nothing</t>
@@ -1297,7 +1300,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1577,7 +1580,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1626,6 +1629,14 @@
       </c>
       <c r="B41" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/brand_rules.xlsx
+++ b/brand_rules.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="44">
   <si>
     <t>关键词</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>Itel</t>
+  </si>
+  <si>
+    <t>Lenovo</t>
   </si>
 </sst>
 </file>
@@ -1300,7 +1303,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1639,6 +1642,14 @@
         <v>42</v>
       </c>
     </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
